--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,19 +680,19 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>34</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-counts.xlsx
+++ b/aircraft/reports/manufacturer-popularity-counts.xlsx
@@ -680,13 +680,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
